--- a/Data/HRV2021_Data.xlsx
+++ b/Data/HRV2021_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nacho\Documents\GitHub\Chained-Indices-Unchained\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4B2949-1E59-4985-A2CD-1FDA64F1BD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DCF3F5-2ED0-4F71-A84B-346CEEA8DA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,7 +664,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -728,28 +728,19 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1723,18 +1714,18 @@
     <col min="98" max="98" width="13.88671875" style="23" bestFit="1" customWidth="1"/>
     <col min="99" max="99" width="12.77734375" style="23" bestFit="1" customWidth="1"/>
     <col min="100" max="104" width="8.88671875" style="23"/>
-    <col min="105" max="105" width="21.77734375" style="33" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="21.5546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="25.21875" style="33" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="25" style="33" bestFit="1" customWidth="1"/>
-    <col min="109" max="110" width="25" style="33" customWidth="1"/>
-    <col min="111" max="112" width="8.88671875" style="33"/>
-    <col min="113" max="113" width="21.5546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="19.77734375" style="33" bestFit="1" customWidth="1"/>
-    <col min="115" max="16384" width="8.88671875" style="33"/>
+    <col min="105" max="105" width="21.77734375" style="23" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="21.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="25.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="25" style="23" bestFit="1" customWidth="1"/>
+    <col min="109" max="110" width="25" style="23" customWidth="1"/>
+    <col min="111" max="112" width="8.88671875" style="23"/>
+    <col min="113" max="113" width="21.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="19.77734375" style="23" bestFit="1" customWidth="1"/>
+    <col min="115" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2051,10 +2042,10 @@
       <c r="DD1" s="30"/>
       <c r="DE1" s="30"/>
       <c r="DF1" s="30"/>
-      <c r="DI1" s="34"/>
-      <c r="DJ1" s="34"/>
+      <c r="DI1" s="31"/>
+      <c r="DJ1" s="31"/>
     </row>
-    <row r="2" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1947</v>
       </c>
@@ -2367,10 +2358,10 @@
         <v>1</v>
       </c>
       <c r="CZ2" s="6"/>
-      <c r="DI2" s="35"/>
-      <c r="DJ2" s="36"/>
+      <c r="DI2" s="32"/>
+      <c r="DJ2" s="11"/>
     </row>
-    <row r="3" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1948</v>
       </c>
@@ -2689,10 +2680,10 @@
         <v>0.98601273843223736</v>
       </c>
       <c r="CZ3" s="6"/>
-      <c r="DI3" s="37"/>
-      <c r="DJ3" s="36"/>
+      <c r="DI3" s="33"/>
+      <c r="DJ3" s="11"/>
     </row>
-    <row r="4" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1949</v>
       </c>
@@ -3009,10 +3000,10 @@
         <v>0.97328459573874482</v>
       </c>
       <c r="CZ4" s="6"/>
-      <c r="DI4" s="37"/>
-      <c r="DJ4" s="36"/>
+      <c r="DI4" s="33"/>
+      <c r="DJ4" s="11"/>
     </row>
-    <row r="5" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1950</v>
       </c>
@@ -3331,10 +3322,10 @@
         <v>1.0146998714116864</v>
       </c>
       <c r="CZ5" s="6"/>
-      <c r="DI5" s="37"/>
-      <c r="DJ5" s="36"/>
+      <c r="DI5" s="33"/>
+      <c r="DJ5" s="11"/>
     </row>
-    <row r="6" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1951</v>
       </c>
@@ -3651,10 +3642,10 @@
         <v>1.0157501259471713</v>
       </c>
       <c r="CZ6" s="6"/>
-      <c r="DI6" s="37"/>
-      <c r="DJ6" s="36"/>
+      <c r="DI6" s="33"/>
+      <c r="DJ6" s="11"/>
     </row>
-    <row r="7" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1952</v>
       </c>
@@ -3971,10 +3962,10 @@
         <v>1.020643644789526</v>
       </c>
       <c r="CZ7" s="6"/>
-      <c r="DI7" s="37"/>
-      <c r="DJ7" s="36"/>
+      <c r="DI7" s="33"/>
+      <c r="DJ7" s="11"/>
     </row>
-    <row r="8" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1953</v>
       </c>
@@ -4291,10 +4282,10 @@
         <v>1.0461721427672477</v>
       </c>
       <c r="CZ8" s="6"/>
-      <c r="DI8" s="37"/>
-      <c r="DJ8" s="36"/>
+      <c r="DI8" s="33"/>
+      <c r="DJ8" s="11"/>
     </row>
-    <row r="9" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1954</v>
       </c>
@@ -4611,10 +4602,10 @@
         <v>1.0445505297077573</v>
       </c>
       <c r="CZ9" s="6"/>
-      <c r="DI9" s="37"/>
-      <c r="DJ9" s="36"/>
+      <c r="DI9" s="33"/>
+      <c r="DJ9" s="11"/>
     </row>
-    <row r="10" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1955</v>
       </c>
@@ -4931,10 +4922,10 @@
         <v>1.0781542273510138</v>
       </c>
       <c r="CZ10" s="6"/>
-      <c r="DI10" s="37"/>
-      <c r="DJ10" s="36"/>
+      <c r="DI10" s="33"/>
+      <c r="DJ10" s="11"/>
     </row>
-    <row r="11" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1956</v>
       </c>
@@ -5251,10 +5242,10 @@
         <v>1.0359145020775968</v>
       </c>
       <c r="CZ11" s="6"/>
-      <c r="DI11" s="37"/>
-      <c r="DJ11" s="36"/>
+      <c r="DI11" s="33"/>
+      <c r="DJ11" s="11"/>
     </row>
-    <row r="12" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1957</v>
       </c>
@@ -5571,10 +5562,10 @@
         <v>1.0348674429339175</v>
       </c>
       <c r="CZ12" s="6"/>
-      <c r="DI12" s="37"/>
-      <c r="DJ12" s="36"/>
+      <c r="DI12" s="33"/>
+      <c r="DJ12" s="11"/>
     </row>
-    <row r="13" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1958</v>
       </c>
@@ -5891,10 +5882,10 @@
         <v>1.0510914904543185</v>
       </c>
       <c r="CZ13" s="6"/>
-      <c r="DI13" s="37"/>
-      <c r="DJ13" s="36"/>
+      <c r="DI13" s="33"/>
+      <c r="DJ13" s="11"/>
     </row>
-    <row r="14" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1959</v>
       </c>
@@ -6211,10 +6202,10 @@
         <v>1.0892086414937645</v>
       </c>
       <c r="CZ14" s="6"/>
-      <c r="DI14" s="37"/>
-      <c r="DJ14" s="36"/>
+      <c r="DI14" s="33"/>
+      <c r="DJ14" s="11"/>
     </row>
-    <row r="15" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1960</v>
       </c>
@@ -6531,10 +6522,10 @@
         <v>1.1005693540559423</v>
       </c>
       <c r="CZ15" s="6"/>
-      <c r="DI15" s="37"/>
-      <c r="DJ15" s="36"/>
+      <c r="DI15" s="33"/>
+      <c r="DJ15" s="11"/>
     </row>
-    <row r="16" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>1961</v>
       </c>
@@ -6851,10 +6842,10 @@
         <v>1.1212255242581564</v>
       </c>
       <c r="CZ16" s="6"/>
-      <c r="DI16" s="37"/>
-      <c r="DJ16" s="36"/>
+      <c r="DI16" s="33"/>
+      <c r="DJ16" s="11"/>
     </row>
-    <row r="17" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1962</v>
       </c>
@@ -7171,10 +7162,10 @@
         <v>1.1577639361922438</v>
       </c>
       <c r="CZ17" s="6"/>
-      <c r="DI17" s="37"/>
-      <c r="DJ17" s="36"/>
+      <c r="DI17" s="33"/>
+      <c r="DJ17" s="11"/>
     </row>
-    <row r="18" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1963</v>
       </c>
@@ -7491,10 +7482,10 @@
         <v>1.1879760592956032</v>
       </c>
       <c r="CZ18" s="6"/>
-      <c r="DI18" s="37"/>
-      <c r="DJ18" s="36"/>
+      <c r="DI18" s="33"/>
+      <c r="DJ18" s="11"/>
     </row>
-    <row r="19" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1964</v>
       </c>
@@ -7811,10 +7802,10 @@
         <v>1.2254989350043595</v>
       </c>
       <c r="CZ19" s="6"/>
-      <c r="DI19" s="37"/>
-      <c r="DJ19" s="36"/>
+      <c r="DI19" s="33"/>
+      <c r="DJ19" s="11"/>
     </row>
-    <row r="20" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>1965</v>
       </c>
@@ -8131,10 +8122,10 @@
         <v>1.2528440477023484</v>
       </c>
       <c r="CZ20" s="6"/>
-      <c r="DI20" s="37"/>
-      <c r="DJ20" s="36"/>
+      <c r="DI20" s="33"/>
+      <c r="DJ20" s="11"/>
     </row>
-    <row r="21" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>1966</v>
       </c>
@@ -8451,10 +8442,10 @@
         <v>1.2788867198532681</v>
       </c>
       <c r="CZ21" s="6"/>
-      <c r="DI21" s="37"/>
-      <c r="DJ21" s="36"/>
+      <c r="DI21" s="33"/>
+      <c r="DJ21" s="11"/>
     </row>
-    <row r="22" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>1967</v>
       </c>
@@ -8771,10 +8762,10 @@
         <v>1.2766196326960562</v>
       </c>
       <c r="CZ22" s="6"/>
-      <c r="DI22" s="37"/>
-      <c r="DJ22" s="36"/>
+      <c r="DI22" s="33"/>
+      <c r="DJ22" s="11"/>
     </row>
-    <row r="23" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>1968</v>
       </c>
@@ -9091,10 +9082,10 @@
         <v>1.2988369825774004</v>
       </c>
       <c r="CZ23" s="6"/>
-      <c r="DI23" s="37"/>
-      <c r="DJ23" s="36"/>
+      <c r="DI23" s="33"/>
+      <c r="DJ23" s="11"/>
     </row>
-    <row r="24" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>1969</v>
       </c>
@@ -9411,10 +9402,10 @@
         <v>1.2887011352748188</v>
       </c>
       <c r="CZ24" s="6"/>
-      <c r="DI24" s="37"/>
-      <c r="DJ24" s="36"/>
+      <c r="DI24" s="33"/>
+      <c r="DJ24" s="11"/>
     </row>
-    <row r="25" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>1970</v>
       </c>
@@ -9731,10 +9722,10 @@
         <v>1.2842987417028178</v>
       </c>
       <c r="CZ25" s="6"/>
-      <c r="DI25" s="37"/>
-      <c r="DJ25" s="36"/>
+      <c r="DI25" s="33"/>
+      <c r="DJ25" s="11"/>
     </row>
-    <row r="26" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>1971</v>
       </c>
@@ -10051,10 +10042,10 @@
         <v>1.2987336303404251</v>
       </c>
       <c r="CZ26" s="6"/>
-      <c r="DI26" s="37"/>
-      <c r="DJ26" s="36"/>
+      <c r="DI26" s="33"/>
+      <c r="DJ26" s="11"/>
     </row>
-    <row r="27" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>1972</v>
       </c>
@@ -10371,10 +10362,10 @@
         <v>1.3174240380486943</v>
       </c>
       <c r="CZ27" s="6"/>
-      <c r="DI27" s="37"/>
-      <c r="DJ27" s="36"/>
+      <c r="DI27" s="33"/>
+      <c r="DJ27" s="11"/>
     </row>
-    <row r="28" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>1973</v>
       </c>
@@ -10691,10 +10682,10 @@
         <v>1.3312338245423465</v>
       </c>
       <c r="CZ28" s="6"/>
-      <c r="DI28" s="37"/>
-      <c r="DJ28" s="36"/>
+      <c r="DI28" s="33"/>
+      <c r="DJ28" s="11"/>
     </row>
-    <row r="29" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>1974</v>
       </c>
@@ -11011,10 +11002,10 @@
         <v>1.2820162593951665</v>
       </c>
       <c r="CZ29" s="6"/>
-      <c r="DI29" s="37"/>
-      <c r="DJ29" s="36"/>
+      <c r="DI29" s="33"/>
+      <c r="DJ29" s="11"/>
     </row>
-    <row r="30" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>1975</v>
       </c>
@@ -11331,10 +11322,10 @@
         <v>1.2552172680792419</v>
       </c>
       <c r="CZ30" s="6"/>
-      <c r="DI30" s="37"/>
-      <c r="DJ30" s="36"/>
+      <c r="DI30" s="33"/>
+      <c r="DJ30" s="11"/>
     </row>
-    <row r="31" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>1976</v>
       </c>
@@ -11651,10 +11642,10 @@
         <v>1.2886050135412737</v>
       </c>
       <c r="CZ31" s="6"/>
-      <c r="DI31" s="37"/>
-      <c r="DJ31" s="36"/>
+      <c r="DI31" s="33"/>
+      <c r="DJ31" s="11"/>
     </row>
-    <row r="32" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>1977</v>
       </c>
@@ -11971,10 +11962,10 @@
         <v>1.2917105208393211</v>
       </c>
       <c r="CZ32" s="6"/>
-      <c r="DI32" s="37"/>
-      <c r="DJ32" s="36"/>
+      <c r="DI32" s="33"/>
+      <c r="DJ32" s="11"/>
     </row>
-    <row r="33" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>1978</v>
       </c>
@@ -12291,10 +12282,10 @@
         <v>1.2903441692860464</v>
       </c>
       <c r="CZ33" s="6"/>
-      <c r="DI33" s="37"/>
-      <c r="DJ33" s="36"/>
+      <c r="DI33" s="33"/>
+      <c r="DJ33" s="11"/>
     </row>
-    <row r="34" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>1979</v>
       </c>
@@ -12611,10 +12602,10 @@
         <v>1.2739707988824231</v>
       </c>
       <c r="CZ34" s="6"/>
-      <c r="DI34" s="37"/>
-      <c r="DJ34" s="36"/>
+      <c r="DI34" s="33"/>
+      <c r="DJ34" s="11"/>
     </row>
-    <row r="35" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>1980</v>
       </c>
@@ -12931,10 +12922,10 @@
         <v>1.2454677912531757</v>
       </c>
       <c r="CZ35" s="6"/>
-      <c r="DI35" s="37"/>
-      <c r="DJ35" s="36"/>
+      <c r="DI35" s="33"/>
+      <c r="DJ35" s="11"/>
     </row>
-    <row r="36" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>1981</v>
       </c>
@@ -13251,10 +13242,10 @@
         <v>1.2481973865532514</v>
       </c>
       <c r="CZ36" s="6"/>
-      <c r="DI36" s="37"/>
-      <c r="DJ36" s="36"/>
+      <c r="DI36" s="33"/>
+      <c r="DJ36" s="11"/>
     </row>
-    <row r="37" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>1982</v>
       </c>
@@ -13571,10 +13562,10 @@
         <v>1.2224386365448474</v>
       </c>
       <c r="CZ37" s="6"/>
-      <c r="DI37" s="37"/>
-      <c r="DJ37" s="36"/>
+      <c r="DI37" s="33"/>
+      <c r="DJ37" s="11"/>
     </row>
-    <row r="38" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>1983</v>
       </c>
@@ -13891,10 +13882,10 @@
         <v>1.2861730333415045</v>
       </c>
       <c r="CZ38" s="6"/>
-      <c r="DI38" s="37"/>
-      <c r="DJ38" s="36"/>
+      <c r="DI38" s="33"/>
+      <c r="DJ38" s="11"/>
     </row>
-    <row r="39" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>1984</v>
       </c>
@@ -14211,10 +14202,10 @@
         <v>1.3439101140044269</v>
       </c>
       <c r="CZ39" s="6"/>
-      <c r="DI39" s="37"/>
-      <c r="DJ39" s="36"/>
+      <c r="DI39" s="33"/>
+      <c r="DJ39" s="11"/>
     </row>
-    <row r="40" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>1985</v>
       </c>
@@ -14531,10 +14522,10 @@
         <v>1.3814887499240927</v>
       </c>
       <c r="CZ40" s="6"/>
-      <c r="DI40" s="37"/>
-      <c r="DJ40" s="36"/>
+      <c r="DI40" s="33"/>
+      <c r="DJ40" s="11"/>
     </row>
-    <row r="41" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>1986</v>
       </c>
@@ -14851,10 +14842,10 @@
         <v>1.3966587140344453</v>
       </c>
       <c r="CZ41" s="6"/>
-      <c r="DI41" s="37"/>
-      <c r="DJ41" s="36"/>
+      <c r="DI41" s="33"/>
+      <c r="DJ41" s="11"/>
     </row>
-    <row r="42" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>1987</v>
       </c>
@@ -15171,10 +15162,10 @@
         <v>1.3990716455776517</v>
       </c>
       <c r="CZ42" s="6"/>
-      <c r="DI42" s="37"/>
-      <c r="DJ42" s="36"/>
+      <c r="DI42" s="33"/>
+      <c r="DJ42" s="11"/>
     </row>
-    <row r="43" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>1988</v>
       </c>
@@ -15491,10 +15482,10 @@
         <v>1.424309193257024</v>
       </c>
       <c r="CZ43" s="6"/>
-      <c r="DI43" s="37"/>
-      <c r="DJ43" s="36"/>
+      <c r="DI43" s="33"/>
+      <c r="DJ43" s="11"/>
     </row>
-    <row r="44" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>1989</v>
       </c>
@@ -15811,10 +15802,10 @@
         <v>1.4512905354818049</v>
       </c>
       <c r="CZ44" s="6"/>
-      <c r="DI44" s="37"/>
-      <c r="DJ44" s="36"/>
+      <c r="DI44" s="33"/>
+      <c r="DJ44" s="11"/>
     </row>
-    <row r="45" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>1990</v>
       </c>
@@ -16131,10 +16122,10 @@
         <v>1.4664841605027277</v>
       </c>
       <c r="CZ45" s="6"/>
-      <c r="DI45" s="37"/>
-      <c r="DJ45" s="36"/>
+      <c r="DI45" s="33"/>
+      <c r="DJ45" s="11"/>
     </row>
-    <row r="46" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>1991</v>
       </c>
@@ -16451,10 +16442,10 @@
         <v>1.4798240548188353</v>
       </c>
       <c r="CZ46" s="6"/>
-      <c r="DI46" s="37"/>
-      <c r="DJ46" s="36"/>
+      <c r="DI46" s="33"/>
+      <c r="DJ46" s="11"/>
     </row>
-    <row r="47" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>1992</v>
       </c>
@@ -16771,10 +16762,10 @@
         <v>1.5418147636901136</v>
       </c>
       <c r="CZ47" s="6"/>
-      <c r="DI47" s="37"/>
-      <c r="DJ47" s="36"/>
+      <c r="DI47" s="33"/>
+      <c r="DJ47" s="11"/>
     </row>
-    <row r="48" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>1993</v>
       </c>
@@ -17091,10 +17082,10 @@
         <v>1.5560883068225482</v>
       </c>
       <c r="CZ48" s="6"/>
-      <c r="DI48" s="37"/>
-      <c r="DJ48" s="36"/>
+      <c r="DI48" s="33"/>
+      <c r="DJ48" s="11"/>
     </row>
-    <row r="49" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>1994</v>
       </c>
@@ -17411,10 +17402,10 @@
         <v>1.5782089621684157</v>
       </c>
       <c r="CZ49" s="6"/>
-      <c r="DI49" s="37"/>
-      <c r="DJ49" s="36"/>
+      <c r="DI49" s="33"/>
+      <c r="DJ49" s="11"/>
     </row>
-    <row r="50" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>1995</v>
       </c>
@@ -17731,10 +17722,10 @@
         <v>1.574122866948926</v>
       </c>
       <c r="CZ50" s="6"/>
-      <c r="DI50" s="37"/>
-      <c r="DJ50" s="36"/>
+      <c r="DI50" s="33"/>
+      <c r="DJ50" s="11"/>
     </row>
-    <row r="51" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>1996</v>
       </c>
@@ -18051,10 +18042,10 @@
         <v>1.6151418350656104</v>
       </c>
       <c r="CZ51" s="6"/>
-      <c r="DI51" s="37"/>
-      <c r="DJ51" s="36"/>
+      <c r="DI51" s="33"/>
+      <c r="DJ51" s="11"/>
     </row>
-    <row r="52" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>1997</v>
       </c>
@@ -18371,16 +18362,16 @@
         <v>1.6428506284674627</v>
       </c>
       <c r="CZ52" s="6"/>
-      <c r="DA52" s="32"/>
-      <c r="DB52" s="32"/>
-      <c r="DC52" s="32"/>
-      <c r="DD52" s="32"/>
-      <c r="DE52" s="32"/>
-      <c r="DF52" s="32"/>
-      <c r="DI52" s="37"/>
-      <c r="DJ52" s="36"/>
+      <c r="DA52" s="7"/>
+      <c r="DB52" s="7"/>
+      <c r="DC52" s="7"/>
+      <c r="DD52" s="7"/>
+      <c r="DE52" s="7"/>
+      <c r="DF52" s="7"/>
+      <c r="DI52" s="33"/>
+      <c r="DJ52" s="11"/>
     </row>
-    <row r="53" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>1998</v>
       </c>
@@ -18697,16 +18688,16 @@
         <v>1.6738392211225741</v>
       </c>
       <c r="CZ53" s="6"/>
-      <c r="DA53" s="32"/>
-      <c r="DB53" s="32"/>
-      <c r="DC53" s="32"/>
-      <c r="DD53" s="32"/>
-      <c r="DE53" s="32"/>
-      <c r="DF53" s="32"/>
-      <c r="DI53" s="37"/>
-      <c r="DJ53" s="36"/>
+      <c r="DA53" s="7"/>
+      <c r="DB53" s="7"/>
+      <c r="DC53" s="7"/>
+      <c r="DD53" s="7"/>
+      <c r="DE53" s="7"/>
+      <c r="DF53" s="7"/>
+      <c r="DI53" s="33"/>
+      <c r="DJ53" s="11"/>
     </row>
-    <row r="54" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>1999</v>
       </c>
@@ -19023,16 +19014,16 @@
         <v>1.7083186712916045</v>
       </c>
       <c r="CZ54" s="6"/>
-      <c r="DA54" s="32"/>
-      <c r="DB54" s="32"/>
-      <c r="DC54" s="32"/>
-      <c r="DD54" s="32"/>
-      <c r="DE54" s="32"/>
-      <c r="DF54" s="32"/>
-      <c r="DI54" s="37"/>
-      <c r="DJ54" s="36"/>
+      <c r="DA54" s="7"/>
+      <c r="DB54" s="7"/>
+      <c r="DC54" s="7"/>
+      <c r="DD54" s="7"/>
+      <c r="DE54" s="7"/>
+      <c r="DF54" s="7"/>
+      <c r="DI54" s="33"/>
+      <c r="DJ54" s="11"/>
     </row>
-    <row r="55" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>2000</v>
       </c>
@@ -19349,16 +19340,16 @@
         <v>1.7285746554404666</v>
       </c>
       <c r="CZ55" s="6"/>
-      <c r="DA55" s="32"/>
-      <c r="DB55" s="32"/>
-      <c r="DC55" s="32"/>
-      <c r="DD55" s="32"/>
-      <c r="DE55" s="32"/>
-      <c r="DF55" s="32"/>
-      <c r="DI55" s="37"/>
-      <c r="DJ55" s="36"/>
+      <c r="DA55" s="7"/>
+      <c r="DB55" s="7"/>
+      <c r="DC55" s="7"/>
+      <c r="DD55" s="7"/>
+      <c r="DE55" s="7"/>
+      <c r="DF55" s="7"/>
+      <c r="DI55" s="33"/>
+      <c r="DJ55" s="11"/>
     </row>
-    <row r="56" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>2001</v>
       </c>
@@ -19675,16 +19666,16 @@
         <v>1.7397676545511394</v>
       </c>
       <c r="CZ56" s="6"/>
-      <c r="DA56" s="32"/>
-      <c r="DB56" s="32"/>
-      <c r="DC56" s="32"/>
-      <c r="DD56" s="32"/>
-      <c r="DE56" s="32"/>
-      <c r="DF56" s="32"/>
-      <c r="DI56" s="37"/>
-      <c r="DJ56" s="36"/>
+      <c r="DA56" s="7"/>
+      <c r="DB56" s="7"/>
+      <c r="DC56" s="7"/>
+      <c r="DD56" s="7"/>
+      <c r="DE56" s="7"/>
+      <c r="DF56" s="7"/>
+      <c r="DI56" s="33"/>
+      <c r="DJ56" s="11"/>
     </row>
-    <row r="57" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>2002</v>
       </c>
@@ -20001,16 +19992,16 @@
         <v>1.7736177072199617</v>
       </c>
       <c r="CZ57" s="6"/>
-      <c r="DA57" s="32"/>
-      <c r="DB57" s="32"/>
-      <c r="DC57" s="32"/>
-      <c r="DD57" s="32"/>
-      <c r="DE57" s="32"/>
-      <c r="DF57" s="32"/>
-      <c r="DI57" s="37"/>
-      <c r="DJ57" s="36"/>
+      <c r="DA57" s="7"/>
+      <c r="DB57" s="7"/>
+      <c r="DC57" s="7"/>
+      <c r="DD57" s="7"/>
+      <c r="DE57" s="7"/>
+      <c r="DF57" s="7"/>
+      <c r="DI57" s="33"/>
+      <c r="DJ57" s="11"/>
     </row>
-    <row r="58" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>2003</v>
       </c>
@@ -20327,16 +20318,16 @@
         <v>1.8215049782454418</v>
       </c>
       <c r="CZ58" s="6"/>
-      <c r="DA58" s="32"/>
-      <c r="DB58" s="32"/>
-      <c r="DC58" s="32"/>
-      <c r="DD58" s="32"/>
-      <c r="DE58" s="32"/>
-      <c r="DF58" s="32"/>
-      <c r="DI58" s="37"/>
-      <c r="DJ58" s="36"/>
+      <c r="DA58" s="7"/>
+      <c r="DB58" s="7"/>
+      <c r="DC58" s="7"/>
+      <c r="DD58" s="7"/>
+      <c r="DE58" s="7"/>
+      <c r="DF58" s="7"/>
+      <c r="DI58" s="33"/>
+      <c r="DJ58" s="11"/>
     </row>
-    <row r="59" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>2004</v>
       </c>
@@ -20653,16 +20644,16 @@
         <v>1.8484753570307095</v>
       </c>
       <c r="CZ59" s="6"/>
-      <c r="DA59" s="32"/>
-      <c r="DB59" s="32"/>
-      <c r="DC59" s="32"/>
-      <c r="DD59" s="32"/>
-      <c r="DE59" s="32"/>
-      <c r="DF59" s="32"/>
-      <c r="DI59" s="37"/>
-      <c r="DJ59" s="36"/>
+      <c r="DA59" s="7"/>
+      <c r="DB59" s="7"/>
+      <c r="DC59" s="7"/>
+      <c r="DD59" s="7"/>
+      <c r="DE59" s="7"/>
+      <c r="DF59" s="7"/>
+      <c r="DI59" s="33"/>
+      <c r="DJ59" s="11"/>
     </row>
-    <row r="60" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>2005</v>
       </c>
@@ -20979,16 +20970,16 @@
         <v>1.8493169670000826</v>
       </c>
       <c r="CZ60" s="6"/>
-      <c r="DA60" s="32"/>
-      <c r="DB60" s="32"/>
-      <c r="DC60" s="32"/>
-      <c r="DD60" s="32"/>
-      <c r="DE60" s="32"/>
-      <c r="DF60" s="32"/>
-      <c r="DI60" s="37"/>
-      <c r="DJ60" s="36"/>
+      <c r="DA60" s="7"/>
+      <c r="DB60" s="7"/>
+      <c r="DC60" s="7"/>
+      <c r="DD60" s="7"/>
+      <c r="DE60" s="7"/>
+      <c r="DF60" s="7"/>
+      <c r="DI60" s="33"/>
+      <c r="DJ60" s="11"/>
     </row>
-    <row r="61" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>2006</v>
       </c>
@@ -21305,16 +21296,16 @@
         <v>1.8335496523126125</v>
       </c>
       <c r="CZ61" s="6"/>
-      <c r="DA61" s="32"/>
-      <c r="DB61" s="32"/>
-      <c r="DC61" s="32"/>
-      <c r="DD61" s="32"/>
-      <c r="DE61" s="32"/>
-      <c r="DF61" s="32"/>
-      <c r="DI61" s="37"/>
-      <c r="DJ61" s="36"/>
+      <c r="DA61" s="7"/>
+      <c r="DB61" s="7"/>
+      <c r="DC61" s="7"/>
+      <c r="DD61" s="7"/>
+      <c r="DE61" s="7"/>
+      <c r="DF61" s="7"/>
+      <c r="DI61" s="33"/>
+      <c r="DJ61" s="11"/>
     </row>
-    <row r="62" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>2007</v>
       </c>
@@ -21631,16 +21622,16 @@
         <v>1.8430852381279481</v>
       </c>
       <c r="CZ62" s="6"/>
-      <c r="DA62" s="32"/>
-      <c r="DB62" s="32"/>
-      <c r="DC62" s="32"/>
-      <c r="DD62" s="32"/>
-      <c r="DE62" s="32"/>
-      <c r="DF62" s="32"/>
-      <c r="DI62" s="37"/>
-      <c r="DJ62" s="36"/>
+      <c r="DA62" s="7"/>
+      <c r="DB62" s="7"/>
+      <c r="DC62" s="7"/>
+      <c r="DD62" s="7"/>
+      <c r="DE62" s="7"/>
+      <c r="DF62" s="7"/>
+      <c r="DI62" s="33"/>
+      <c r="DJ62" s="11"/>
     </row>
-    <row r="63" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>2008</v>
       </c>
@@ -21957,16 +21948,16 @@
         <v>1.8376151511131944</v>
       </c>
       <c r="CZ63" s="6"/>
-      <c r="DA63" s="32"/>
-      <c r="DB63" s="32"/>
-      <c r="DC63" s="32"/>
-      <c r="DD63" s="32"/>
-      <c r="DE63" s="32"/>
-      <c r="DF63" s="32"/>
-      <c r="DI63" s="37"/>
-      <c r="DJ63" s="36"/>
+      <c r="DA63" s="7"/>
+      <c r="DB63" s="7"/>
+      <c r="DC63" s="7"/>
+      <c r="DD63" s="7"/>
+      <c r="DE63" s="7"/>
+      <c r="DF63" s="7"/>
+      <c r="DI63" s="33"/>
+      <c r="DJ63" s="11"/>
     </row>
-    <row r="64" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>2009</v>
       </c>
@@ -22283,16 +22274,16 @@
         <v>1.8524389159947183</v>
       </c>
       <c r="CZ64" s="6"/>
-      <c r="DA64" s="32"/>
-      <c r="DB64" s="32"/>
-      <c r="DC64" s="32"/>
-      <c r="DD64" s="32"/>
-      <c r="DE64" s="32"/>
-      <c r="DF64" s="32"/>
-      <c r="DI64" s="37"/>
-      <c r="DJ64" s="36"/>
+      <c r="DA64" s="7"/>
+      <c r="DB64" s="7"/>
+      <c r="DC64" s="7"/>
+      <c r="DD64" s="7"/>
+      <c r="DE64" s="7"/>
+      <c r="DF64" s="7"/>
+      <c r="DI64" s="33"/>
+      <c r="DJ64" s="11"/>
     </row>
-    <row r="65" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>2010</v>
       </c>
@@ -22609,16 +22600,16 @@
         <v>1.9431137220755132</v>
       </c>
       <c r="CZ65" s="6"/>
-      <c r="DA65" s="32"/>
-      <c r="DB65" s="32"/>
-      <c r="DC65" s="32"/>
-      <c r="DD65" s="32"/>
-      <c r="DE65" s="32"/>
-      <c r="DF65" s="32"/>
-      <c r="DI65" s="37"/>
-      <c r="DJ65" s="36"/>
+      <c r="DA65" s="7"/>
+      <c r="DB65" s="7"/>
+      <c r="DC65" s="7"/>
+      <c r="DD65" s="7"/>
+      <c r="DE65" s="7"/>
+      <c r="DF65" s="7"/>
+      <c r="DI65" s="33"/>
+      <c r="DJ65" s="11"/>
     </row>
-    <row r="66" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>2011</v>
       </c>
@@ -22935,16 +22926,16 @@
         <v>1.9544416935018152</v>
       </c>
       <c r="CZ66" s="6"/>
-      <c r="DA66" s="32"/>
-      <c r="DB66" s="32"/>
-      <c r="DC66" s="32"/>
-      <c r="DD66" s="32"/>
-      <c r="DE66" s="32"/>
-      <c r="DF66" s="32"/>
-      <c r="DI66" s="37"/>
-      <c r="DJ66" s="36"/>
+      <c r="DA66" s="7"/>
+      <c r="DB66" s="7"/>
+      <c r="DC66" s="7"/>
+      <c r="DD66" s="7"/>
+      <c r="DE66" s="7"/>
+      <c r="DF66" s="7"/>
+      <c r="DI66" s="33"/>
+      <c r="DJ66" s="11"/>
     </row>
-    <row r="67" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>2012</v>
       </c>
@@ -23261,16 +23252,16 @@
         <v>1.9730624350567294</v>
       </c>
       <c r="CZ67" s="6"/>
-      <c r="DA67" s="32"/>
-      <c r="DB67" s="32"/>
-      <c r="DC67" s="32"/>
-      <c r="DD67" s="32"/>
-      <c r="DE67" s="32"/>
-      <c r="DF67" s="32"/>
-      <c r="DI67" s="37"/>
-      <c r="DJ67" s="36"/>
+      <c r="DA67" s="7"/>
+      <c r="DB67" s="7"/>
+      <c r="DC67" s="7"/>
+      <c r="DD67" s="7"/>
+      <c r="DE67" s="7"/>
+      <c r="DF67" s="7"/>
+      <c r="DI67" s="33"/>
+      <c r="DJ67" s="11"/>
     </row>
-    <row r="68" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>2013</v>
       </c>
@@ -23587,16 +23578,16 @@
         <v>1.9917511479535741</v>
       </c>
       <c r="CZ68" s="6"/>
-      <c r="DA68" s="32"/>
-      <c r="DB68" s="32"/>
-      <c r="DC68" s="32"/>
-      <c r="DD68" s="32"/>
-      <c r="DE68" s="32"/>
-      <c r="DF68" s="32"/>
-      <c r="DI68" s="37"/>
-      <c r="DJ68" s="36"/>
+      <c r="DA68" s="7"/>
+      <c r="DB68" s="7"/>
+      <c r="DC68" s="7"/>
+      <c r="DD68" s="7"/>
+      <c r="DE68" s="7"/>
+      <c r="DF68" s="7"/>
+      <c r="DI68" s="33"/>
+      <c r="DJ68" s="11"/>
     </row>
-    <row r="69" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>2014</v>
       </c>
@@ -23913,16 +23904,16 @@
         <v>2.0072171679931232</v>
       </c>
       <c r="CZ69" s="6"/>
-      <c r="DA69" s="32"/>
-      <c r="DB69" s="32"/>
-      <c r="DC69" s="32"/>
-      <c r="DD69" s="32"/>
-      <c r="DE69" s="32"/>
-      <c r="DF69" s="32"/>
-      <c r="DI69" s="37"/>
-      <c r="DJ69" s="36"/>
+      <c r="DA69" s="7"/>
+      <c r="DB69" s="7"/>
+      <c r="DC69" s="7"/>
+      <c r="DD69" s="7"/>
+      <c r="DE69" s="7"/>
+      <c r="DF69" s="7"/>
+      <c r="DI69" s="33"/>
+      <c r="DJ69" s="11"/>
     </row>
-    <row r="70" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>2015</v>
       </c>
@@ -24239,16 +24230,16 @@
         <v>2.0253169381745719</v>
       </c>
       <c r="CZ70" s="6"/>
-      <c r="DA70" s="32"/>
-      <c r="DB70" s="32"/>
-      <c r="DC70" s="32"/>
-      <c r="DD70" s="32"/>
-      <c r="DE70" s="32"/>
-      <c r="DF70" s="32"/>
-      <c r="DI70" s="37"/>
-      <c r="DJ70" s="36"/>
+      <c r="DA70" s="7"/>
+      <c r="DB70" s="7"/>
+      <c r="DC70" s="7"/>
+      <c r="DD70" s="7"/>
+      <c r="DE70" s="7"/>
+      <c r="DF70" s="7"/>
+      <c r="DI70" s="33"/>
+      <c r="DJ70" s="11"/>
     </row>
-    <row r="71" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>2016</v>
       </c>
@@ -24565,16 +24556,16 @@
         <v>2.0411966939684234</v>
       </c>
       <c r="CZ71" s="6"/>
-      <c r="DA71" s="32"/>
-      <c r="DB71" s="32"/>
-      <c r="DC71" s="32"/>
-      <c r="DD71" s="32"/>
-      <c r="DE71" s="32"/>
-      <c r="DF71" s="32"/>
-      <c r="DI71" s="37"/>
-      <c r="DJ71" s="36"/>
+      <c r="DA71" s="7"/>
+      <c r="DB71" s="7"/>
+      <c r="DC71" s="7"/>
+      <c r="DD71" s="7"/>
+      <c r="DE71" s="7"/>
+      <c r="DF71" s="7"/>
+      <c r="DI71" s="33"/>
+      <c r="DJ71" s="11"/>
     </row>
-    <row r="72" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>2017</v>
       </c>
@@ -24891,16 +24882,16 @@
         <v>2.0620976460985578</v>
       </c>
       <c r="CZ72" s="6"/>
-      <c r="DA72" s="32"/>
-      <c r="DB72" s="32"/>
-      <c r="DC72" s="32"/>
-      <c r="DD72" s="32"/>
-      <c r="DE72" s="32"/>
-      <c r="DF72" s="32"/>
-      <c r="DI72" s="37"/>
-      <c r="DJ72" s="36"/>
+      <c r="DA72" s="7"/>
+      <c r="DB72" s="7"/>
+      <c r="DC72" s="7"/>
+      <c r="DD72" s="7"/>
+      <c r="DE72" s="7"/>
+      <c r="DF72" s="7"/>
+      <c r="DI72" s="33"/>
+      <c r="DJ72" s="11"/>
     </row>
-    <row r="73" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>2018</v>
       </c>
@@ -25063,74 +25054,26 @@
         <f t="shared" si="15"/>
         <v>0.88068566496722078</v>
       </c>
-      <c r="BA73"/>
-      <c r="BB73"/>
-      <c r="BC73"/>
-      <c r="BD73"/>
-      <c r="BE73"/>
-      <c r="BF73"/>
-      <c r="BG73"/>
-      <c r="BH73"/>
-      <c r="BI73"/>
-      <c r="BJ73"/>
-      <c r="BK73"/>
-      <c r="BL73"/>
-      <c r="BM73"/>
-      <c r="BN73"/>
-      <c r="BO73"/>
-      <c r="BP73"/>
-      <c r="BQ73"/>
-      <c r="BR73"/>
-      <c r="BS73"/>
-      <c r="BT73"/>
-      <c r="BU73"/>
-      <c r="BV73"/>
-      <c r="BW73"/>
-      <c r="BX73"/>
-      <c r="BY73"/>
-      <c r="BZ73"/>
-      <c r="CA73"/>
-      <c r="CB73"/>
-      <c r="CC73"/>
-      <c r="CD73"/>
-      <c r="CE73"/>
-      <c r="CF73"/>
-      <c r="CG73"/>
-      <c r="CH73"/>
-      <c r="CI73"/>
-      <c r="CJ73"/>
-      <c r="CK73"/>
-      <c r="CL73"/>
-      <c r="CM73"/>
-      <c r="CN73"/>
-      <c r="CO73"/>
-      <c r="CP73"/>
-      <c r="CQ73"/>
-      <c r="CR73"/>
-      <c r="CS73"/>
       <c r="CT73" s="7">
         <v>1.9416589676097435</v>
       </c>
       <c r="CU73" s="7">
         <v>1.3200489774365141</v>
       </c>
-      <c r="CV73"/>
-      <c r="CW73"/>
-      <c r="CX73"/>
       <c r="CY73" s="7">
         <v>2.0886816997750528</v>
       </c>
       <c r="CZ73" s="6"/>
-      <c r="DA73" s="32"/>
-      <c r="DB73" s="32"/>
-      <c r="DC73" s="32"/>
-      <c r="DD73" s="32"/>
-      <c r="DE73" s="32"/>
-      <c r="DF73" s="32"/>
-      <c r="DI73" s="37"/>
-      <c r="DJ73" s="36"/>
+      <c r="DA73" s="7"/>
+      <c r="DB73" s="7"/>
+      <c r="DC73" s="7"/>
+      <c r="DD73" s="7"/>
+      <c r="DE73" s="7"/>
+      <c r="DF73" s="7"/>
+      <c r="DI73" s="33"/>
+      <c r="DJ73" s="11"/>
     </row>
-    <row r="74" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>2019</v>
       </c>
@@ -25293,74 +25236,26 @@
         <f t="shared" ref="AZ74:AZ78" si="24">T74/(T74+R74)</f>
         <v>0.88558590266358661</v>
       </c>
-      <c r="BA74"/>
-      <c r="BB74"/>
-      <c r="BC74"/>
-      <c r="BD74"/>
-      <c r="BE74"/>
-      <c r="BF74"/>
-      <c r="BG74"/>
-      <c r="BH74"/>
-      <c r="BI74"/>
-      <c r="BJ74"/>
-      <c r="BK74"/>
-      <c r="BL74"/>
-      <c r="BM74"/>
-      <c r="BN74"/>
-      <c r="BO74"/>
-      <c r="BP74"/>
-      <c r="BQ74"/>
-      <c r="BR74"/>
-      <c r="BS74"/>
-      <c r="BT74"/>
-      <c r="BU74"/>
-      <c r="BV74"/>
-      <c r="BW74"/>
-      <c r="BX74"/>
-      <c r="BY74"/>
-      <c r="BZ74"/>
-      <c r="CA74"/>
-      <c r="CB74"/>
-      <c r="CC74"/>
-      <c r="CD74"/>
-      <c r="CE74"/>
-      <c r="CF74"/>
-      <c r="CG74"/>
-      <c r="CH74"/>
-      <c r="CI74"/>
-      <c r="CJ74"/>
-      <c r="CK74"/>
-      <c r="CL74"/>
-      <c r="CM74"/>
-      <c r="CN74"/>
-      <c r="CO74"/>
-      <c r="CP74"/>
-      <c r="CQ74"/>
-      <c r="CR74"/>
-      <c r="CS74"/>
       <c r="CT74" s="7">
         <v>1.9314168440652164</v>
       </c>
       <c r="CU74" s="7">
         <v>1.3333111329227267</v>
       </c>
-      <c r="CV74"/>
-      <c r="CW74"/>
-      <c r="CX74"/>
       <c r="CY74" s="7">
         <v>2.1059339959962093</v>
       </c>
       <c r="CZ74" s="6"/>
-      <c r="DA74" s="32"/>
-      <c r="DB74" s="32"/>
-      <c r="DC74" s="32"/>
-      <c r="DD74" s="32"/>
-      <c r="DE74" s="32"/>
-      <c r="DF74" s="32"/>
-      <c r="DI74" s="37"/>
-      <c r="DJ74" s="36"/>
+      <c r="DA74" s="7"/>
+      <c r="DB74" s="7"/>
+      <c r="DC74" s="7"/>
+      <c r="DD74" s="7"/>
+      <c r="DE74" s="7"/>
+      <c r="DF74" s="7"/>
+      <c r="DI74" s="33"/>
+      <c r="DJ74" s="11"/>
     </row>
-    <row r="75" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>2020</v>
       </c>
@@ -25523,74 +25418,26 @@
         <f t="shared" si="24"/>
         <v>0.8918009246591817</v>
       </c>
-      <c r="BA75"/>
-      <c r="BB75"/>
-      <c r="BC75"/>
-      <c r="BD75"/>
-      <c r="BE75"/>
-      <c r="BF75"/>
-      <c r="BG75"/>
-      <c r="BH75"/>
-      <c r="BI75"/>
-      <c r="BJ75"/>
-      <c r="BK75"/>
-      <c r="BL75"/>
-      <c r="BM75"/>
-      <c r="BN75"/>
-      <c r="BO75"/>
-      <c r="BP75"/>
-      <c r="BQ75"/>
-      <c r="BR75"/>
-      <c r="BS75"/>
-      <c r="BT75"/>
-      <c r="BU75"/>
-      <c r="BV75"/>
-      <c r="BW75"/>
-      <c r="BX75"/>
-      <c r="BY75"/>
-      <c r="BZ75"/>
-      <c r="CA75"/>
-      <c r="CB75"/>
-      <c r="CC75"/>
-      <c r="CD75"/>
-      <c r="CE75"/>
-      <c r="CF75"/>
-      <c r="CG75"/>
-      <c r="CH75"/>
-      <c r="CI75"/>
-      <c r="CJ75"/>
-      <c r="CK75"/>
-      <c r="CL75"/>
-      <c r="CM75"/>
-      <c r="CN75"/>
-      <c r="CO75"/>
-      <c r="CP75"/>
-      <c r="CQ75"/>
-      <c r="CR75"/>
-      <c r="CS75"/>
       <c r="CT75" s="7">
         <v>1.9271587960387428</v>
       </c>
       <c r="CU75" s="7">
         <v>1.3236158420940836</v>
       </c>
-      <c r="CV75"/>
-      <c r="CW75"/>
-      <c r="CX75"/>
       <c r="CY75" s="7">
         <v>2.0919389087402256</v>
       </c>
       <c r="CZ75" s="6"/>
-      <c r="DA75" s="32"/>
-      <c r="DB75" s="32"/>
-      <c r="DC75" s="32"/>
-      <c r="DD75" s="32"/>
-      <c r="DE75" s="32"/>
-      <c r="DF75" s="32"/>
-      <c r="DI75" s="37"/>
-      <c r="DJ75" s="36"/>
+      <c r="DA75" s="7"/>
+      <c r="DB75" s="7"/>
+      <c r="DC75" s="7"/>
+      <c r="DD75" s="7"/>
+      <c r="DE75" s="7"/>
+      <c r="DF75" s="7"/>
+      <c r="DI75" s="33"/>
+      <c r="DJ75" s="11"/>
     </row>
-    <row r="76" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>2021</v>
       </c>
@@ -25753,74 +25600,26 @@
         <f t="shared" si="24"/>
         <v>0.88269426441259502</v>
       </c>
-      <c r="BA76"/>
-      <c r="BB76"/>
-      <c r="BC76"/>
-      <c r="BD76"/>
-      <c r="BE76"/>
-      <c r="BF76"/>
-      <c r="BG76"/>
-      <c r="BH76"/>
-      <c r="BI76"/>
-      <c r="BJ76"/>
-      <c r="BK76"/>
-      <c r="BL76"/>
-      <c r="BM76"/>
-      <c r="BN76"/>
-      <c r="BO76"/>
-      <c r="BP76"/>
-      <c r="BQ76"/>
-      <c r="BR76"/>
-      <c r="BS76"/>
-      <c r="BT76"/>
-      <c r="BU76"/>
-      <c r="BV76"/>
-      <c r="BW76"/>
-      <c r="BX76"/>
-      <c r="BY76"/>
-      <c r="BZ76"/>
-      <c r="CA76"/>
-      <c r="CB76"/>
-      <c r="CC76"/>
-      <c r="CD76"/>
-      <c r="CE76"/>
-      <c r="CF76"/>
-      <c r="CG76"/>
-      <c r="CH76"/>
-      <c r="CI76"/>
-      <c r="CJ76"/>
-      <c r="CK76"/>
-      <c r="CL76"/>
-      <c r="CM76"/>
-      <c r="CN76"/>
-      <c r="CO76"/>
-      <c r="CP76"/>
-      <c r="CQ76"/>
-      <c r="CR76"/>
-      <c r="CS76"/>
       <c r="CT76" s="7">
         <v>1.9648328270893161</v>
       </c>
       <c r="CU76" s="7">
         <v>1.3704154619559092</v>
       </c>
-      <c r="CV76"/>
-      <c r="CW76"/>
-      <c r="CX76"/>
       <c r="CY76" s="7">
         <v>2.1763934363126305</v>
       </c>
       <c r="CZ76" s="6"/>
-      <c r="DA76" s="32"/>
-      <c r="DB76" s="32"/>
-      <c r="DC76" s="32"/>
-      <c r="DD76" s="32"/>
-      <c r="DE76" s="32"/>
-      <c r="DF76" s="32"/>
-      <c r="DI76" s="37"/>
-      <c r="DJ76" s="36"/>
+      <c r="DA76" s="7"/>
+      <c r="DB76" s="7"/>
+      <c r="DC76" s="7"/>
+      <c r="DD76" s="7"/>
+      <c r="DE76" s="7"/>
+      <c r="DF76" s="7"/>
+      <c r="DI76" s="33"/>
+      <c r="DJ76" s="11"/>
     </row>
-    <row r="77" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>2022</v>
       </c>
@@ -25983,74 +25782,26 @@
         <f t="shared" si="24"/>
         <v>0.87453705079136279</v>
       </c>
-      <c r="BA77"/>
-      <c r="BB77"/>
-      <c r="BC77"/>
-      <c r="BD77"/>
-      <c r="BE77"/>
-      <c r="BF77"/>
-      <c r="BG77"/>
-      <c r="BH77"/>
-      <c r="BI77"/>
-      <c r="BJ77"/>
-      <c r="BK77"/>
-      <c r="BL77"/>
-      <c r="BM77"/>
-      <c r="BN77"/>
-      <c r="BO77"/>
-      <c r="BP77"/>
-      <c r="BQ77"/>
-      <c r="BR77"/>
-      <c r="BS77"/>
-      <c r="BT77"/>
-      <c r="BU77"/>
-      <c r="BV77"/>
-      <c r="BW77"/>
-      <c r="BX77"/>
-      <c r="BY77"/>
-      <c r="BZ77"/>
-      <c r="CA77"/>
-      <c r="CB77"/>
-      <c r="CC77"/>
-      <c r="CD77"/>
-      <c r="CE77"/>
-      <c r="CF77"/>
-      <c r="CG77"/>
-      <c r="CH77"/>
-      <c r="CI77"/>
-      <c r="CJ77"/>
-      <c r="CK77"/>
-      <c r="CL77"/>
-      <c r="CM77"/>
-      <c r="CN77"/>
-      <c r="CO77"/>
-      <c r="CP77"/>
-      <c r="CQ77"/>
-      <c r="CR77"/>
-      <c r="CS77"/>
       <c r="CT77" s="7">
         <v>1.8781482536768745</v>
       </c>
       <c r="CU77" s="7">
         <v>1.364903925690836</v>
       </c>
-      <c r="CV77"/>
-      <c r="CW77"/>
-      <c r="CX77"/>
       <c r="CY77" s="7">
         <v>2.1449880655580333</v>
       </c>
       <c r="CZ77" s="6"/>
-      <c r="DA77" s="32"/>
-      <c r="DB77" s="32"/>
-      <c r="DC77" s="32"/>
-      <c r="DD77" s="32"/>
-      <c r="DE77" s="32"/>
-      <c r="DF77" s="32"/>
-      <c r="DI77" s="37"/>
-      <c r="DJ77" s="36"/>
+      <c r="DA77" s="7"/>
+      <c r="DB77" s="7"/>
+      <c r="DC77" s="7"/>
+      <c r="DD77" s="7"/>
+      <c r="DE77" s="7"/>
+      <c r="DF77" s="7"/>
+      <c r="DI77" s="33"/>
+      <c r="DJ77" s="11"/>
     </row>
-    <row r="78" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>2023</v>
       </c>
@@ -26213,74 +25964,26 @@
         <f t="shared" si="24"/>
         <v>0.88050042269057771</v>
       </c>
-      <c r="BA78"/>
-      <c r="BB78"/>
-      <c r="BC78"/>
-      <c r="BD78"/>
-      <c r="BE78"/>
-      <c r="BF78"/>
-      <c r="BG78"/>
-      <c r="BH78"/>
-      <c r="BI78"/>
-      <c r="BJ78"/>
-      <c r="BK78"/>
-      <c r="BL78"/>
-      <c r="BM78"/>
-      <c r="BN78"/>
-      <c r="BO78"/>
-      <c r="BP78"/>
-      <c r="BQ78"/>
-      <c r="BR78"/>
-      <c r="BS78"/>
-      <c r="BT78"/>
-      <c r="BU78"/>
-      <c r="BV78"/>
-      <c r="BW78"/>
-      <c r="BX78"/>
-      <c r="BY78"/>
-      <c r="BZ78"/>
-      <c r="CA78"/>
-      <c r="CB78"/>
-      <c r="CC78"/>
-      <c r="CD78"/>
-      <c r="CE78"/>
-      <c r="CF78"/>
-      <c r="CG78"/>
-      <c r="CH78"/>
-      <c r="CI78"/>
-      <c r="CJ78"/>
-      <c r="CK78"/>
-      <c r="CL78"/>
-      <c r="CM78"/>
-      <c r="CN78"/>
-      <c r="CO78"/>
-      <c r="CP78"/>
-      <c r="CQ78"/>
-      <c r="CR78"/>
-      <c r="CS78"/>
       <c r="CT78" s="7">
         <v>1.9244900047123736</v>
       </c>
       <c r="CU78" s="7">
         <v>1.3766101081188256</v>
       </c>
-      <c r="CV78"/>
-      <c r="CW78"/>
-      <c r="CX78"/>
       <c r="CY78" s="7">
         <v>2.1784198594712381</v>
       </c>
       <c r="CZ78" s="6"/>
-      <c r="DA78" s="32"/>
-      <c r="DB78" s="32"/>
-      <c r="DC78" s="32"/>
-      <c r="DD78" s="32"/>
-      <c r="DE78" s="32"/>
-      <c r="DF78" s="32"/>
-      <c r="DI78" s="37"/>
-      <c r="DJ78" s="36"/>
+      <c r="DA78" s="7"/>
+      <c r="DB78" s="7"/>
+      <c r="DC78" s="7"/>
+      <c r="DD78" s="7"/>
+      <c r="DE78" s="7"/>
+      <c r="DF78" s="7"/>
+      <c r="DI78" s="33"/>
+      <c r="DJ78" s="11"/>
     </row>
-    <row r="79" spans="1:114" s="31" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17"/>
       <c r="B79" s="18"/>
       <c r="C79" s="19"/>
@@ -26386,861 +26089,55 @@
       <c r="CY79" s="21"/>
       <c r="CZ79" s="16"/>
     </row>
-    <row r="80" spans="1:114" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
-      <c r="N80" s="23"/>
-      <c r="O80" s="23"/>
-      <c r="P80" s="23"/>
-      <c r="Q80" s="23"/>
-      <c r="R80" s="23"/>
-      <c r="S80" s="23"/>
-      <c r="T80" s="23"/>
-      <c r="U80" s="23"/>
-      <c r="V80" s="23"/>
-      <c r="W80" s="23"/>
-      <c r="X80" s="23"/>
-      <c r="Y80" s="23"/>
-      <c r="Z80" s="23"/>
-      <c r="AA80" s="23"/>
-      <c r="AB80" s="23"/>
-      <c r="AC80" s="23"/>
-      <c r="AD80" s="23"/>
-      <c r="AE80" s="23"/>
-      <c r="AF80" s="23"/>
-      <c r="AG80" s="23"/>
-      <c r="AH80" s="23"/>
-      <c r="AI80" s="23"/>
-      <c r="AJ80" s="23"/>
-      <c r="AK80" s="23"/>
-      <c r="AL80" s="23"/>
-      <c r="AM80" s="23"/>
-      <c r="AN80" s="23"/>
+    <row r="80" spans="1:114" x14ac:dyDescent="0.3">
       <c r="AO80" s="24"/>
       <c r="AP80" s="25"/>
       <c r="AQ80" s="24"/>
       <c r="AR80" s="26"/>
       <c r="AS80" s="26"/>
       <c r="AT80" s="24"/>
-      <c r="AU80" s="23"/>
-      <c r="AV80" s="23"/>
-      <c r="AW80" s="23"/>
-      <c r="AX80" s="23"/>
-      <c r="AY80" s="23"/>
-      <c r="AZ80" s="23"/>
-      <c r="BA80" s="23"/>
-      <c r="BB80" s="23"/>
-      <c r="BC80" s="23"/>
-      <c r="BD80" s="23"/>
-      <c r="BE80" s="23"/>
-      <c r="BF80" s="23"/>
-      <c r="BG80" s="23"/>
-      <c r="BH80" s="23"/>
-      <c r="BI80" s="23"/>
-      <c r="BJ80" s="23"/>
-      <c r="BK80" s="23"/>
-      <c r="BL80" s="23"/>
-      <c r="BM80" s="23"/>
-      <c r="BN80" s="23"/>
-      <c r="BO80" s="23"/>
-      <c r="BP80" s="23"/>
-      <c r="BQ80" s="23"/>
-      <c r="BR80" s="23"/>
-      <c r="BS80" s="23"/>
-      <c r="BT80" s="23"/>
-      <c r="BU80" s="23"/>
-      <c r="BV80" s="23"/>
-      <c r="BW80" s="23"/>
-      <c r="BX80" s="23"/>
-      <c r="BY80" s="23"/>
-      <c r="BZ80" s="23"/>
-      <c r="CA80" s="23"/>
-      <c r="CB80" s="23"/>
-      <c r="CC80" s="23"/>
-      <c r="CD80" s="23"/>
-      <c r="CE80" s="23"/>
-      <c r="CF80" s="23"/>
-      <c r="CG80" s="23"/>
-      <c r="CH80" s="23"/>
-      <c r="CI80" s="23"/>
-      <c r="CJ80" s="23"/>
-      <c r="CK80" s="23"/>
-      <c r="CL80" s="23"/>
-      <c r="CM80" s="23"/>
-      <c r="CN80" s="23"/>
-      <c r="CO80" s="23"/>
-      <c r="CP80" s="23"/>
-      <c r="CQ80" s="23"/>
-      <c r="CR80" s="23"/>
-      <c r="CS80" s="23"/>
-      <c r="CT80" s="23"/>
-      <c r="CU80" s="23"/>
-      <c r="CV80" s="23"/>
-      <c r="CW80" s="23"/>
-      <c r="CX80" s="23"/>
-      <c r="CY80" s="23"/>
-      <c r="CZ80" s="23"/>
-      <c r="DI80" s="38"/>
     </row>
-    <row r="81" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="22"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
+    <row r="81" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G81" s="15"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="23"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
-      <c r="R81" s="23"/>
-      <c r="S81" s="23"/>
-      <c r="T81" s="23"/>
-      <c r="U81" s="23"/>
-      <c r="V81" s="23"/>
-      <c r="W81" s="23"/>
-      <c r="X81" s="23"/>
-      <c r="Y81" s="23"/>
-      <c r="Z81" s="23"/>
-      <c r="AA81" s="23"/>
-      <c r="AB81" s="23"/>
-      <c r="AC81" s="23"/>
-      <c r="AD81" s="23"/>
-      <c r="AE81" s="23"/>
-      <c r="AF81" s="23"/>
-      <c r="AG81" s="23"/>
-      <c r="AH81" s="23"/>
-      <c r="AI81" s="23"/>
-      <c r="AJ81" s="23"/>
-      <c r="AK81" s="23"/>
-      <c r="AL81" s="23"/>
       <c r="AM81" s="24"/>
-      <c r="AN81" s="23"/>
       <c r="AO81" s="24"/>
       <c r="AP81" s="25"/>
       <c r="AQ81" s="24"/>
       <c r="AR81" s="25"/>
       <c r="AS81" s="25"/>
       <c r="AT81" s="24"/>
-      <c r="AU81" s="23"/>
-      <c r="AV81" s="23"/>
-      <c r="AW81" s="23"/>
-      <c r="AX81" s="23"/>
-      <c r="AY81" s="23"/>
-      <c r="AZ81" s="23"/>
-      <c r="BA81" s="23"/>
-      <c r="BB81" s="23"/>
-      <c r="BC81" s="23"/>
-      <c r="BD81" s="23"/>
-      <c r="BE81" s="23"/>
-      <c r="BF81" s="23"/>
-      <c r="BG81" s="23"/>
-      <c r="BH81" s="23"/>
-      <c r="BI81" s="23"/>
-      <c r="BJ81" s="23"/>
-      <c r="BK81" s="23"/>
-      <c r="BL81" s="23"/>
-      <c r="BM81" s="23"/>
-      <c r="BN81" s="23"/>
-      <c r="BO81" s="23"/>
-      <c r="BP81" s="23"/>
-      <c r="BQ81" s="23"/>
-      <c r="BR81" s="23"/>
-      <c r="BS81" s="23"/>
-      <c r="BT81" s="23"/>
-      <c r="BU81" s="23"/>
-      <c r="BV81" s="23"/>
-      <c r="BW81" s="23"/>
-      <c r="BX81" s="23"/>
-      <c r="BY81" s="23"/>
-      <c r="BZ81" s="23"/>
-      <c r="CA81" s="23"/>
-      <c r="CB81" s="23"/>
-      <c r="CC81" s="23"/>
-      <c r="CD81" s="23"/>
-      <c r="CE81" s="23"/>
-      <c r="CF81" s="23"/>
-      <c r="CG81" s="23"/>
-      <c r="CH81" s="23"/>
-      <c r="CI81" s="23"/>
-      <c r="CJ81" s="23"/>
-      <c r="CK81" s="23"/>
-      <c r="CL81" s="23"/>
-      <c r="CM81" s="23"/>
-      <c r="CN81" s="23"/>
-      <c r="CO81" s="23"/>
-      <c r="CP81" s="23"/>
-      <c r="CQ81" s="23"/>
-      <c r="CR81" s="23"/>
-      <c r="CS81" s="23"/>
-      <c r="CT81" s="23"/>
-      <c r="CU81" s="23"/>
-      <c r="CV81" s="23"/>
-      <c r="CW81" s="23"/>
-      <c r="CX81" s="23"/>
-      <c r="CY81" s="23"/>
-      <c r="CZ81" s="23"/>
-      <c r="DI81" s="38"/>
     </row>
-    <row r="82" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="22"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
+    <row r="82" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G82" s="15"/>
-      <c r="H82" s="23"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="23"/>
-      <c r="K82" s="23"/>
-      <c r="L82" s="23"/>
-      <c r="M82" s="23"/>
-      <c r="N82" s="23"/>
-      <c r="O82" s="23"/>
-      <c r="P82" s="23"/>
-      <c r="Q82" s="23"/>
-      <c r="R82" s="23"/>
-      <c r="S82" s="23"/>
-      <c r="T82" s="23"/>
-      <c r="U82" s="23"/>
-      <c r="V82" s="23"/>
-      <c r="W82" s="23"/>
-      <c r="X82" s="23"/>
-      <c r="Y82" s="23"/>
-      <c r="Z82" s="23"/>
-      <c r="AA82" s="23"/>
-      <c r="AB82" s="23"/>
-      <c r="AC82" s="23"/>
-      <c r="AD82" s="23"/>
-      <c r="AE82" s="23"/>
-      <c r="AF82" s="23"/>
-      <c r="AG82" s="23"/>
-      <c r="AH82" s="23"/>
-      <c r="AI82" s="23"/>
-      <c r="AJ82" s="23"/>
-      <c r="AK82" s="23"/>
-      <c r="AL82" s="23"/>
       <c r="AM82" s="24"/>
-      <c r="AN82" s="23"/>
       <c r="AO82" s="24"/>
       <c r="AP82" s="25"/>
       <c r="AQ82" s="24"/>
       <c r="AR82" s="25"/>
       <c r="AS82" s="25"/>
       <c r="AT82" s="24"/>
-      <c r="AU82" s="23"/>
-      <c r="AV82" s="23"/>
-      <c r="AW82" s="23"/>
-      <c r="AX82" s="23"/>
-      <c r="AY82" s="23"/>
-      <c r="AZ82" s="23"/>
-      <c r="BA82" s="23"/>
-      <c r="BB82" s="23"/>
-      <c r="BC82" s="23"/>
-      <c r="BD82" s="23"/>
-      <c r="BE82" s="23"/>
-      <c r="BF82" s="23"/>
-      <c r="BG82" s="23"/>
-      <c r="BH82" s="23"/>
-      <c r="BI82" s="23"/>
-      <c r="BJ82" s="23"/>
-      <c r="BK82" s="23"/>
-      <c r="BL82" s="23"/>
-      <c r="BM82" s="23"/>
-      <c r="BN82" s="23"/>
-      <c r="BO82" s="23"/>
-      <c r="BP82" s="23"/>
-      <c r="BQ82" s="23"/>
-      <c r="BR82" s="23"/>
-      <c r="BS82" s="23"/>
-      <c r="BT82" s="23"/>
-      <c r="BU82" s="23"/>
-      <c r="BV82" s="23"/>
-      <c r="BW82" s="23"/>
-      <c r="BX82" s="23"/>
-      <c r="BY82" s="23"/>
-      <c r="BZ82" s="23"/>
-      <c r="CA82" s="23"/>
-      <c r="CB82" s="23"/>
-      <c r="CC82" s="23"/>
-      <c r="CD82" s="23"/>
-      <c r="CE82" s="23"/>
-      <c r="CF82" s="23"/>
-      <c r="CG82" s="23"/>
-      <c r="CH82" s="23"/>
-      <c r="CI82" s="23"/>
-      <c r="CJ82" s="23"/>
-      <c r="CK82" s="23"/>
-      <c r="CL82" s="23"/>
-      <c r="CM82" s="23"/>
-      <c r="CN82" s="23"/>
-      <c r="CO82" s="23"/>
-      <c r="CP82" s="23"/>
-      <c r="CQ82" s="23"/>
-      <c r="CR82" s="23"/>
-      <c r="CS82" s="23"/>
-      <c r="CT82" s="23"/>
-      <c r="CU82" s="23"/>
-      <c r="CV82" s="23"/>
-      <c r="CW82" s="23"/>
-      <c r="CX82" s="23"/>
-      <c r="CY82" s="23"/>
-      <c r="CZ82" s="23"/>
-      <c r="DI82" s="38"/>
     </row>
-    <row r="83" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="22"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
+    <row r="83" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G83" s="15"/>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="23"/>
-      <c r="K83" s="23"/>
-      <c r="L83" s="23"/>
-      <c r="M83" s="23"/>
-      <c r="N83" s="23"/>
-      <c r="O83" s="23"/>
-      <c r="P83" s="23"/>
-      <c r="Q83" s="23"/>
-      <c r="R83" s="23"/>
-      <c r="S83" s="23"/>
-      <c r="T83" s="23"/>
-      <c r="U83" s="23"/>
-      <c r="V83" s="23"/>
-      <c r="W83" s="23"/>
-      <c r="X83" s="23"/>
-      <c r="Y83" s="23"/>
-      <c r="Z83" s="23"/>
-      <c r="AA83" s="23"/>
-      <c r="AB83" s="23"/>
-      <c r="AC83" s="23"/>
-      <c r="AD83" s="23"/>
-      <c r="AE83" s="23"/>
-      <c r="AF83" s="23"/>
-      <c r="AG83" s="23"/>
-      <c r="AH83" s="23"/>
-      <c r="AI83" s="23"/>
-      <c r="AJ83" s="23"/>
-      <c r="AK83" s="23"/>
-      <c r="AL83" s="23"/>
       <c r="AM83" s="24"/>
-      <c r="AN83" s="23"/>
       <c r="AO83" s="24"/>
       <c r="AP83" s="25"/>
       <c r="AQ83" s="24"/>
       <c r="AR83" s="26"/>
       <c r="AS83" s="26"/>
       <c r="AT83" s="24"/>
-      <c r="AU83" s="23"/>
-      <c r="AV83" s="23"/>
-      <c r="AW83" s="23"/>
-      <c r="AX83" s="23"/>
-      <c r="AY83" s="23"/>
-      <c r="AZ83" s="23"/>
-      <c r="BA83" s="23"/>
-      <c r="BB83" s="23"/>
-      <c r="BC83" s="23"/>
-      <c r="BD83" s="23"/>
-      <c r="BE83" s="23"/>
-      <c r="BF83" s="23"/>
-      <c r="BG83" s="23"/>
-      <c r="BH83" s="23"/>
-      <c r="BI83" s="23"/>
-      <c r="BJ83" s="23"/>
-      <c r="BK83" s="23"/>
-      <c r="BL83" s="23"/>
-      <c r="BM83" s="23"/>
-      <c r="BN83" s="23"/>
-      <c r="BO83" s="23"/>
-      <c r="BP83" s="23"/>
-      <c r="BQ83" s="23"/>
-      <c r="BR83" s="23"/>
-      <c r="BS83" s="23"/>
-      <c r="BT83" s="23"/>
-      <c r="BU83" s="23"/>
-      <c r="BV83" s="23"/>
-      <c r="BW83" s="23"/>
-      <c r="BX83" s="23"/>
-      <c r="BY83" s="23"/>
-      <c r="BZ83" s="23"/>
-      <c r="CA83" s="23"/>
-      <c r="CB83" s="23"/>
-      <c r="CC83" s="23"/>
-      <c r="CD83" s="23"/>
-      <c r="CE83" s="23"/>
-      <c r="CF83" s="23"/>
-      <c r="CG83" s="23"/>
-      <c r="CH83" s="23"/>
-      <c r="CI83" s="23"/>
-      <c r="CJ83" s="23"/>
-      <c r="CK83" s="23"/>
-      <c r="CL83" s="23"/>
-      <c r="CM83" s="23"/>
-      <c r="CN83" s="23"/>
-      <c r="CO83" s="23"/>
-      <c r="CP83" s="23"/>
-      <c r="CQ83" s="23"/>
-      <c r="CR83" s="23"/>
-      <c r="CS83" s="23"/>
-      <c r="CT83" s="23"/>
-      <c r="CU83" s="23"/>
-      <c r="CV83" s="23"/>
-      <c r="CW83" s="23"/>
-      <c r="CX83" s="23"/>
-      <c r="CY83" s="23"/>
-      <c r="CZ83" s="23"/>
-      <c r="DI83" s="38"/>
     </row>
-    <row r="84" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="22"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
+    <row r="84" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G84" s="15"/>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="23"/>
-      <c r="K84" s="23"/>
-      <c r="L84" s="23"/>
-      <c r="M84" s="23"/>
-      <c r="N84" s="23"/>
-      <c r="O84" s="23"/>
-      <c r="P84" s="23"/>
-      <c r="Q84" s="23"/>
-      <c r="R84" s="23"/>
-      <c r="S84" s="23"/>
-      <c r="T84" s="23"/>
-      <c r="U84" s="23"/>
-      <c r="V84" s="23"/>
-      <c r="W84" s="23"/>
-      <c r="X84" s="23"/>
-      <c r="Y84" s="23"/>
-      <c r="Z84" s="23"/>
-      <c r="AA84" s="23"/>
-      <c r="AB84" s="23"/>
-      <c r="AC84" s="23"/>
-      <c r="AD84" s="23"/>
-      <c r="AE84" s="23"/>
-      <c r="AF84" s="23"/>
-      <c r="AG84" s="23"/>
-      <c r="AH84" s="23"/>
-      <c r="AI84" s="23"/>
-      <c r="AJ84" s="23"/>
-      <c r="AK84" s="23"/>
-      <c r="AL84" s="23"/>
-      <c r="AM84" s="23"/>
-      <c r="AN84" s="23"/>
-      <c r="AO84" s="23"/>
-      <c r="AP84" s="23"/>
-      <c r="AQ84" s="23"/>
-      <c r="AR84" s="23"/>
-      <c r="AS84" s="23"/>
-      <c r="AT84" s="23"/>
-      <c r="AU84" s="23"/>
-      <c r="AV84" s="23"/>
-      <c r="AW84" s="23"/>
-      <c r="AX84" s="23"/>
-      <c r="AY84" s="23"/>
-      <c r="AZ84" s="23"/>
-      <c r="BA84" s="23"/>
-      <c r="BB84" s="23"/>
-      <c r="BC84" s="23"/>
-      <c r="BD84" s="23"/>
-      <c r="BE84" s="23"/>
-      <c r="BF84" s="23"/>
-      <c r="BG84" s="23"/>
-      <c r="BH84" s="23"/>
-      <c r="BI84" s="23"/>
-      <c r="BJ84" s="23"/>
-      <c r="BK84" s="23"/>
-      <c r="BL84" s="23"/>
-      <c r="BM84" s="23"/>
-      <c r="BN84" s="23"/>
-      <c r="BO84" s="23"/>
-      <c r="BP84" s="23"/>
-      <c r="BQ84" s="23"/>
-      <c r="BR84" s="23"/>
-      <c r="BS84" s="23"/>
-      <c r="BT84" s="23"/>
-      <c r="BU84" s="23"/>
-      <c r="BV84" s="23"/>
-      <c r="BW84" s="23"/>
-      <c r="BX84" s="23"/>
-      <c r="BY84" s="23"/>
-      <c r="BZ84" s="23"/>
-      <c r="CA84" s="23"/>
-      <c r="CB84" s="23"/>
-      <c r="CC84" s="23"/>
-      <c r="CD84" s="23"/>
-      <c r="CE84" s="23"/>
-      <c r="CF84" s="23"/>
-      <c r="CG84" s="23"/>
-      <c r="CH84" s="23"/>
-      <c r="CI84" s="23"/>
-      <c r="CJ84" s="23"/>
-      <c r="CK84" s="23"/>
-      <c r="CL84" s="23"/>
-      <c r="CM84" s="23"/>
-      <c r="CN84" s="23"/>
-      <c r="CO84" s="23"/>
-      <c r="CP84" s="23"/>
-      <c r="CQ84" s="23"/>
-      <c r="CR84" s="23"/>
-      <c r="CS84" s="23"/>
-      <c r="CT84" s="23"/>
-      <c r="CU84" s="23"/>
-      <c r="CV84" s="23"/>
-      <c r="CW84" s="23"/>
-      <c r="CX84" s="23"/>
-      <c r="CY84" s="23"/>
-      <c r="CZ84" s="23"/>
-      <c r="DI84" s="38"/>
     </row>
-    <row r="85" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="22"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
+    <row r="85" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G85" s="27"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23"/>
-      <c r="J85" s="23"/>
-      <c r="K85" s="23"/>
-      <c r="L85" s="23"/>
-      <c r="M85" s="23"/>
-      <c r="N85" s="23"/>
-      <c r="O85" s="23"/>
-      <c r="P85" s="23"/>
-      <c r="Q85" s="23"/>
-      <c r="R85" s="23"/>
-      <c r="S85" s="23"/>
-      <c r="T85" s="23"/>
-      <c r="U85" s="23"/>
-      <c r="V85" s="23"/>
-      <c r="W85" s="23"/>
-      <c r="X85" s="23"/>
-      <c r="Y85" s="23"/>
-      <c r="Z85" s="23"/>
-      <c r="AA85" s="23"/>
-      <c r="AB85" s="23"/>
-      <c r="AC85" s="23"/>
-      <c r="AD85" s="23"/>
-      <c r="AE85" s="23"/>
-      <c r="AF85" s="23"/>
-      <c r="AG85" s="23"/>
-      <c r="AH85" s="23"/>
-      <c r="AI85" s="23"/>
-      <c r="AJ85" s="23"/>
-      <c r="AK85" s="23"/>
-      <c r="AL85" s="23"/>
-      <c r="AM85" s="23"/>
-      <c r="AN85" s="23"/>
-      <c r="AO85" s="23"/>
-      <c r="AP85" s="23"/>
-      <c r="AQ85" s="23"/>
-      <c r="AR85" s="23"/>
-      <c r="AS85" s="23"/>
-      <c r="AT85" s="23"/>
-      <c r="AU85" s="23"/>
-      <c r="AV85" s="23"/>
-      <c r="AW85" s="23"/>
-      <c r="AX85" s="23"/>
-      <c r="AY85" s="23"/>
-      <c r="AZ85" s="23"/>
-      <c r="BA85" s="23"/>
-      <c r="BB85" s="23"/>
-      <c r="BC85" s="23"/>
-      <c r="BD85" s="23"/>
-      <c r="BE85" s="23"/>
-      <c r="BF85" s="23"/>
-      <c r="BG85" s="23"/>
-      <c r="BH85" s="23"/>
-      <c r="BI85" s="23"/>
-      <c r="BJ85" s="23"/>
-      <c r="BK85" s="23"/>
-      <c r="BL85" s="23"/>
-      <c r="BM85" s="23"/>
-      <c r="BN85" s="23"/>
-      <c r="BO85" s="23"/>
-      <c r="BP85" s="23"/>
-      <c r="BQ85" s="23"/>
-      <c r="BR85" s="23"/>
-      <c r="BS85" s="23"/>
-      <c r="BT85" s="23"/>
-      <c r="BU85" s="23"/>
-      <c r="BV85" s="23"/>
-      <c r="BW85" s="23"/>
-      <c r="BX85" s="23"/>
-      <c r="BY85" s="23"/>
-      <c r="BZ85" s="23"/>
-      <c r="CA85" s="23"/>
-      <c r="CB85" s="23"/>
-      <c r="CC85" s="23"/>
-      <c r="CD85" s="23"/>
-      <c r="CE85" s="23"/>
-      <c r="CF85" s="23"/>
-      <c r="CG85" s="23"/>
-      <c r="CH85" s="23"/>
-      <c r="CI85" s="23"/>
-      <c r="CJ85" s="23"/>
-      <c r="CK85" s="23"/>
-      <c r="CL85" s="23"/>
-      <c r="CM85" s="23"/>
-      <c r="CN85" s="23"/>
-      <c r="CO85" s="23"/>
-      <c r="CP85" s="23"/>
-      <c r="CQ85" s="23"/>
-      <c r="CR85" s="23"/>
-      <c r="CS85" s="23"/>
-      <c r="CT85" s="23"/>
-      <c r="CU85" s="23"/>
-      <c r="CV85" s="23"/>
-      <c r="CW85" s="23"/>
-      <c r="CX85" s="23"/>
-      <c r="CY85" s="23"/>
-      <c r="CZ85" s="23"/>
-      <c r="DI85" s="38"/>
     </row>
-    <row r="86" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="22"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
+    <row r="86" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G86" s="15"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="23"/>
-      <c r="K86" s="23"/>
-      <c r="L86" s="23"/>
-      <c r="M86" s="23"/>
-      <c r="N86" s="23"/>
-      <c r="O86" s="23"/>
-      <c r="P86" s="23"/>
-      <c r="Q86" s="23"/>
-      <c r="R86" s="23"/>
-      <c r="S86" s="23"/>
-      <c r="T86" s="23"/>
-      <c r="U86" s="23"/>
-      <c r="V86" s="23"/>
-      <c r="W86" s="23"/>
-      <c r="X86" s="23"/>
-      <c r="Y86" s="23"/>
-      <c r="Z86" s="23"/>
-      <c r="AA86" s="23"/>
-      <c r="AB86" s="23"/>
-      <c r="AC86" s="23"/>
-      <c r="AD86" s="23"/>
-      <c r="AE86" s="23"/>
-      <c r="AF86" s="23"/>
-      <c r="AG86" s="23"/>
-      <c r="AH86" s="23"/>
-      <c r="AI86" s="23"/>
-      <c r="AJ86" s="23"/>
-      <c r="AK86" s="23"/>
-      <c r="AL86" s="23"/>
-      <c r="AM86" s="23"/>
-      <c r="AN86" s="23"/>
-      <c r="AO86" s="23"/>
-      <c r="AP86" s="23"/>
-      <c r="AQ86" s="23"/>
-      <c r="AR86" s="23"/>
-      <c r="AS86" s="23"/>
-      <c r="AT86" s="23"/>
-      <c r="AU86" s="23"/>
-      <c r="AV86" s="23"/>
-      <c r="AW86" s="23"/>
-      <c r="AX86" s="23"/>
-      <c r="AY86" s="23"/>
-      <c r="AZ86" s="23"/>
-      <c r="BA86" s="23"/>
-      <c r="BB86" s="23"/>
-      <c r="BC86" s="23"/>
-      <c r="BD86" s="23"/>
-      <c r="BE86" s="23"/>
-      <c r="BF86" s="23"/>
-      <c r="BG86" s="23"/>
-      <c r="BH86" s="23"/>
-      <c r="BI86" s="23"/>
-      <c r="BJ86" s="23"/>
-      <c r="BK86" s="23"/>
-      <c r="BL86" s="23"/>
-      <c r="BM86" s="23"/>
-      <c r="BN86" s="23"/>
-      <c r="BO86" s="23"/>
-      <c r="BP86" s="23"/>
-      <c r="BQ86" s="23"/>
-      <c r="BR86" s="23"/>
-      <c r="BS86" s="23"/>
-      <c r="BT86" s="23"/>
-      <c r="BU86" s="23"/>
-      <c r="BV86" s="23"/>
-      <c r="BW86" s="23"/>
-      <c r="BX86" s="23"/>
-      <c r="BY86" s="23"/>
-      <c r="BZ86" s="23"/>
-      <c r="CA86" s="23"/>
-      <c r="CB86" s="23"/>
-      <c r="CC86" s="23"/>
-      <c r="CD86" s="23"/>
-      <c r="CE86" s="23"/>
-      <c r="CF86" s="23"/>
-      <c r="CG86" s="23"/>
-      <c r="CH86" s="23"/>
-      <c r="CI86" s="23"/>
-      <c r="CJ86" s="23"/>
-      <c r="CK86" s="23"/>
-      <c r="CL86" s="23"/>
-      <c r="CM86" s="23"/>
-      <c r="CN86" s="23"/>
-      <c r="CO86" s="23"/>
-      <c r="CP86" s="23"/>
-      <c r="CQ86" s="23"/>
-      <c r="CR86" s="23"/>
-      <c r="CS86" s="23"/>
-      <c r="CT86" s="23"/>
-      <c r="CU86" s="23"/>
-      <c r="CV86" s="23"/>
-      <c r="CW86" s="23"/>
-      <c r="CX86" s="23"/>
-      <c r="CY86" s="23"/>
-      <c r="CZ86" s="23"/>
-      <c r="DI86" s="38"/>
     </row>
-    <row r="87" spans="1:113" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="22"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
+    <row r="87" spans="7:46" x14ac:dyDescent="0.3">
       <c r="G87" s="28"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="23"/>
-      <c r="K87" s="23"/>
-      <c r="L87" s="23"/>
-      <c r="M87" s="23"/>
-      <c r="N87" s="23"/>
-      <c r="O87" s="23"/>
-      <c r="P87" s="23"/>
-      <c r="Q87" s="23"/>
-      <c r="R87" s="23"/>
-      <c r="S87" s="23"/>
-      <c r="T87" s="23"/>
-      <c r="U87" s="23"/>
-      <c r="V87" s="23"/>
-      <c r="W87" s="23"/>
-      <c r="X87" s="23"/>
-      <c r="Y87" s="23"/>
-      <c r="Z87" s="23"/>
-      <c r="AA87" s="23"/>
-      <c r="AB87" s="23"/>
-      <c r="AC87" s="23"/>
-      <c r="AD87" s="23"/>
-      <c r="AE87" s="23"/>
-      <c r="AF87" s="23"/>
-      <c r="AG87" s="23"/>
-      <c r="AH87" s="23"/>
-      <c r="AI87" s="23"/>
-      <c r="AJ87" s="23"/>
-      <c r="AK87" s="23"/>
-      <c r="AL87" s="23"/>
-      <c r="AM87" s="23"/>
-      <c r="AN87" s="23"/>
-      <c r="AO87" s="23"/>
-      <c r="AP87" s="23"/>
-      <c r="AQ87" s="23"/>
-      <c r="AR87" s="23"/>
-      <c r="AS87" s="23"/>
-      <c r="AT87" s="23"/>
-      <c r="AU87" s="23"/>
-      <c r="AV87" s="23"/>
-      <c r="AW87" s="23"/>
-      <c r="AX87" s="23"/>
-      <c r="AY87" s="23"/>
-      <c r="AZ87" s="23"/>
-      <c r="BA87" s="23"/>
-      <c r="BB87" s="23"/>
-      <c r="BC87" s="23"/>
-      <c r="BD87" s="23"/>
-      <c r="BE87" s="23"/>
-      <c r="BF87" s="23"/>
-      <c r="BG87" s="23"/>
-      <c r="BH87" s="23"/>
-      <c r="BI87" s="23"/>
-      <c r="BJ87" s="23"/>
-      <c r="BK87" s="23"/>
-      <c r="BL87" s="23"/>
-      <c r="BM87" s="23"/>
-      <c r="BN87" s="23"/>
-      <c r="BO87" s="23"/>
-      <c r="BP87" s="23"/>
-      <c r="BQ87" s="23"/>
-      <c r="BR87" s="23"/>
-      <c r="BS87" s="23"/>
-      <c r="BT87" s="23"/>
-      <c r="BU87" s="23"/>
-      <c r="BV87" s="23"/>
-      <c r="BW87" s="23"/>
-      <c r="BX87" s="23"/>
-      <c r="BY87" s="23"/>
-      <c r="BZ87" s="23"/>
-      <c r="CA87" s="23"/>
-      <c r="CB87" s="23"/>
-      <c r="CC87" s="23"/>
-      <c r="CD87" s="23"/>
-      <c r="CE87" s="23"/>
-      <c r="CF87" s="23"/>
-      <c r="CG87" s="23"/>
-      <c r="CH87" s="23"/>
-      <c r="CI87" s="23"/>
-      <c r="CJ87" s="23"/>
-      <c r="CK87" s="23"/>
-      <c r="CL87" s="23"/>
-      <c r="CM87" s="23"/>
-      <c r="CN87" s="23"/>
-      <c r="CO87" s="23"/>
-      <c r="CP87" s="23"/>
-      <c r="CQ87" s="23"/>
-      <c r="CR87" s="23"/>
-      <c r="CS87" s="23"/>
-      <c r="CT87" s="23"/>
-      <c r="CU87" s="23"/>
-      <c r="CV87" s="23"/>
-      <c r="CW87" s="23"/>
-      <c r="CX87" s="23"/>
-      <c r="CY87" s="23"/>
-      <c r="CZ87" s="23"/>
-      <c r="DI87" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
